--- a/Training_Plan_July_2026_Detailed.xlsx
+++ b/Training_Plan_July_2026_Detailed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\CanadaLife\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6482F04C-67B5-4A1E-81A3-A539D1D8E4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4846047C-7FDA-4B62-8A52-CDE89E3C790F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -56,9 +56,6 @@
 Spring Boot project structure &amp; annotations
 REST controllers &amp; request/response mapping
 Lab: Hello API</t>
-  </si>
-  <si>
-    <t>JDK 21 LTS; IntelliJ IDEA 2026.1; Maven 3.9.11; Spring Boot 3.5.x</t>
   </si>
   <si>
     <t>2026-07-09</t>
@@ -416,6 +413,12 @@
   </si>
   <si>
     <t>Copilot; GitLab Duo; Databricks</t>
+  </si>
+  <si>
+    <t>JDK 21 LTS; Spring tool suite 2026.1; Maven 3.9.11; Spring Boot 3.5.x</t>
+  </si>
+  <si>
+    <t>Company Portal. No issues</t>
   </si>
 </sst>
 </file>
@@ -450,7 +453,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -473,11 +476,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -486,6 +500,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -790,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="65.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.9296875" bestFit="1" customWidth="1"/>
@@ -801,7 +818,7 @@
     <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="57" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -838,431 +855,434 @@
         <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="57" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6" ht="57" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="57" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="57" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="57" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="114" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Training_Plan_July_2026_Detailed.xlsx
+++ b/Training_Plan_July_2026_Detailed.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4846047C-7FDA-4B62-8A52-CDE89E3C790F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -502,7 +502,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -808,17 +808,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="65.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="65.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.46484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.4609375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.07421875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -838,7 +838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -861,7 +861,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -881,7 +881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -901,7 +901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -915,7 +915,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -929,7 +929,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -949,7 +949,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -969,7 +969,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -989,7 +989,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="102" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>55</v>
       </c>
@@ -1043,7 +1043,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>56</v>
       </c>
@@ -1057,7 +1057,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:7" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>61</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="57" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>71</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>76</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>81</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -1185,7 +1185,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>83</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="57" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>88</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>92</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>97</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="114" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="116.6" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>102</v>
       </c>
